--- a/petme2-ads-agent/outbox/2026-10-04-v2/PETME2-ALL-CAMPAIGNS-V2.xlsx
+++ b/petme2-ads-agent/outbox/2026-10-04-v2/PETME2-ALL-CAMPAIGNS-V2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y422"/>
+  <dimension ref="A1:Y428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4517,36 +4517,26 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>V2-Brand</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>PETME2 | Brand | Exact</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>20261004</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>Manual</t>
+          <t>V2-Competitors</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>V2-Comp-WiFi</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Competitors - 5L WiFi Feeder (low bids)</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>paused</t>
-        </is>
-      </c>
-      <c r="P99" t="n">
-        <v>3</v>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
-        </is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="R99" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="100">
@@ -4557,7 +4547,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4567,17 +4557,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>V2-Brand</t>
+          <t>V2-Competitors</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>V2-Brand-All</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>PETME2 Brand - Exact</t>
+          <t>V2-Comp-WiFi</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -4585,8 +4570,10 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="R100" t="n">
-        <v>0.24</v>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>QO-7VBS-CVT4</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -4597,7 +4584,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4607,12 +4594,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>V2-Brand</t>
+          <t>V2-Competitors</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>V2-Brand-All</t>
+          <t>V2-Comp-WiFi</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -4620,9 +4607,12 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>LW-EZAJ-KKZD</t>
+      <c r="S101" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>asin="B0D44QYZ7Z"</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4624,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4644,12 +4634,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>V2-Brand</t>
+          <t>V2-Competitors</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>V2-Brand-All</t>
+          <t>V2-Comp-WiFi</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -4657,9 +4647,12 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>93-E8EG-20UY</t>
+      <c r="S102" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>asin="B09S8WMJY9"</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4664,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4681,12 +4674,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>V2-Brand</t>
+          <t>V2-Competitors</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>V2-Brand-All</t>
+          <t>V2-Comp-WiFi</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -4694,9 +4687,12 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>QO-7VBS-CVT4</t>
+      <c r="S103" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>asin="B0C5X4N132"</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4704,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Product Targeting</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4718,12 +4714,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>V2-Brand</t>
+          <t>V2-Competitors</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>V2-Brand-All</t>
+          <t>V2-Comp-WiFi</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -4731,9 +4727,12 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>2H-2T1T-CJC3</t>
+      <c r="S104" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>asin="B0GTXN5MJK"</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4744,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4758,19 +4757,32 @@
           <t>V2-Brand</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>V2-Brand-All</t>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>PETME2 | Brand | Exact</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>20261004</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Manual</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>QY-HHE8-0H1B</t>
+          <t>paused</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>3</v>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4794,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4800,15 +4812,18 @@
           <t>V2-Brand-All</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>PETME2 Brand - Exact</t>
+        </is>
+      </c>
       <c r="O106" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>L6-L3S1-I7Q6</t>
-        </is>
+      <c r="R106" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="107">
@@ -4844,7 +4859,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>SD-85ET-IOZ3</t>
+          <t>LW-EZAJ-KKZD</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4896,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>JE-LQEW-9EHL</t>
+          <t>93-E8EG-20UY</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4908,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4916,17 +4931,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S109" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>petme2</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>exact</t>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>QO-7VBS-CVT4</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4945,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4961,17 +4968,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S110" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>petme2 cat feeder</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>exact</t>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>2H-2T1T-CJC3</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4982,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5006,17 +5005,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S111" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T111" t="inlineStr">
-        <is>
-          <t>petme2 cat water fountain</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>exact</t>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>QY-HHE8-0H1B</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5019,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5038,35 +5029,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>V2-KeywordTest</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>PETME2 | Keyword Test | Phrase</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>20261004</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>Manual</t>
+          <t>V2-Brand</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>V2-Brand-All</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>paused</t>
-        </is>
-      </c>
-      <c r="P112" t="n">
-        <v>13</v>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>L6-L3S1-I7Q6</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5056,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5088,7 +5066,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>V2-KeywordTest</t>
+          <t>V2-Brand</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>V2-Brand-All</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -5096,14 +5079,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>petme2</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>negativePhrase</t>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>SD-85ET-IOZ3</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5093,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5125,7 +5103,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>V2-KeywordTest</t>
+          <t>V2-Brand</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>V2-Brand-All</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -5133,14 +5116,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>gravity</t>
-        </is>
-      </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>negativePhrase</t>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>JE-LQEW-9EHL</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5130,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5162,7 +5140,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>V2-KeywordTest</t>
+          <t>V2-Brand</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>V2-Brand-All</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -5170,14 +5153,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S115" t="n">
+        <v>0.24</v>
+      </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>replacement</t>
+          <t>petme2</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>exact</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5175,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5199,7 +5185,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>V2-KeywordTest</t>
+          <t>V2-Brand</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>V2-Brand-All</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -5207,14 +5198,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S116" t="n">
+        <v>0.24</v>
+      </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>petme2 cat feeder</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>exact</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5220,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5236,7 +5230,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>V2-KeywordTest</t>
+          <t>V2-Brand</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>V2-Brand-All</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -5244,14 +5243,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S117" t="n">
+        <v>0.24</v>
+      </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>bird</t>
+          <t>petme2 cat water fountain</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>exact</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5265,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5276,19 +5278,32 @@
           <t>V2-KeywordTest</t>
         </is>
       </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>PETME2 | Keyword Test | Phrase</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>20261004</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>negativePhrase</t>
+          <t>paused</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>13</v>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5335,7 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>slow feeder</t>
+          <t>petme2</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -5357,7 +5372,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>gravity</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -5394,7 +5409,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>wireless</t>
+          <t>replacement</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
@@ -5431,7 +5446,7 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>ceramic</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -5468,7 +5483,7 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>outdoor</t>
+          <t>bird</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
@@ -5505,7 +5520,7 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>heated</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -5542,7 +5557,7 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>large dog</t>
+          <t>slow feeder</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -5579,7 +5594,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>wet food</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -5616,12 +5631,12 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>automatic cat feeder</t>
+          <t>wireless</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -5653,12 +5668,12 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>cat feeder automatic</t>
+          <t>ceramic</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -5690,12 +5705,12 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>cat automatic feeders</t>
+          <t>outdoor</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5742,12 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>automatic pet feeder</t>
+          <t>heated</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -5764,12 +5779,12 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>automatic cat feeder 2 cats</t>
+          <t>large dog</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -5801,12 +5816,12 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>automatic cat feeder for 2 cats</t>
+          <t>wet food</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5853,7 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>timed cat feeder</t>
+          <t>automatic cat feeder</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
@@ -5875,7 +5890,7 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>dual cat feeder</t>
+          <t>cat feeder automatic</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -5912,7 +5927,7 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>automatic cat feeder with camera</t>
+          <t>cat automatic feeders</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
@@ -5949,7 +5964,7 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>cat feeder with camera</t>
+          <t>automatic pet feeder</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -5986,7 +6001,7 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>pet feeder with camera</t>
+          <t>automatic cat feeder 2 cats</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -6023,7 +6038,7 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>automatic dog feeder with camera</t>
+          <t>automatic cat feeder for 2 cats</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
@@ -6060,7 +6075,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>wifi cat feeder</t>
+          <t>timed cat feeder</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -6097,7 +6112,7 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>automatic cat feeder wifi</t>
+          <t>dual cat feeder</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -6134,7 +6149,7 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>cat water fountain</t>
+          <t>automatic cat feeder with camera</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -6171,7 +6186,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>stainless steel cat water fountain</t>
+          <t>cat feeder with camera</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -6208,7 +6223,7 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>cat water fountain stainless steel</t>
+          <t>pet feeder with camera</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
@@ -6245,7 +6260,7 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>cat fountain stainless steel</t>
+          <t>automatic dog feeder with camera</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
@@ -6282,7 +6297,7 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>cat fountain</t>
+          <t>wifi cat feeder</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
@@ -6319,7 +6334,7 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>water fountains for cats indoor</t>
+          <t>automatic cat feeder wifi</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
@@ -6356,7 +6371,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>pet water fountain</t>
+          <t>cat water fountain</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
@@ -6393,7 +6408,7 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>metal cat water fountain</t>
+          <t>stainless steel cat water fountain</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
@@ -6430,7 +6445,7 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>stainless steel pet water fountain</t>
+          <t>cat water fountain stainless steel</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
@@ -6467,7 +6482,7 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>stainless steel dog water fountain</t>
+          <t>cat fountain stainless steel</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
@@ -6504,7 +6519,7 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>water fountain for cats</t>
+          <t>cat fountain</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
@@ -6541,7 +6556,7 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>automatic cat water fountain</t>
+          <t>water fountains for cats indoor</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -6578,7 +6593,7 @@
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>cat water fountain with filter</t>
+          <t>pet water fountain</t>
         </is>
       </c>
       <c r="U153" t="inlineStr">
@@ -6615,7 +6630,7 @@
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>quiet cat water fountain</t>
+          <t>metal cat water fountain</t>
         </is>
       </c>
       <c r="U154" t="inlineStr">
@@ -6652,7 +6667,7 @@
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>small cat water fountain</t>
+          <t>stainless steel pet water fountain</t>
         </is>
       </c>
       <c r="U155" t="inlineStr">
@@ -6669,7 +6684,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6682,23 +6697,20 @@
           <t>V2-KeywordTest</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>V2-Test-DualFeeders</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>Test - Dual Feeders</t>
-        </is>
-      </c>
       <c r="O156" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="R156" t="n">
-        <v>0.4</v>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>stainless steel dog water fountain</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -6709,7 +6721,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6722,19 +6734,19 @@
           <t>V2-KeywordTest</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>V2-Test-DualFeeders</t>
-        </is>
-      </c>
       <c r="O157" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>LW-EZAJ-KKZD</t>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>water fountain for cats</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6758,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6759,19 +6771,19 @@
           <t>V2-KeywordTest</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>V2-Test-DualFeeders</t>
-        </is>
-      </c>
       <c r="O158" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>93-E8EG-20UY</t>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>automatic cat water fountain</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6795,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6796,27 +6808,19 @@
           <t>V2-KeywordTest</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>V2-Test-DualFeeders</t>
-        </is>
-      </c>
       <c r="O159" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="S159" t="n">
-        <v>0.68</v>
-      </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>dual cat feeder</t>
+          <t>cat water fountain with filter</t>
         </is>
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6832,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6841,27 +6845,19 @@
           <t>V2-KeywordTest</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>V2-Test-DualFeeders</t>
-        </is>
-      </c>
       <c r="O160" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="S160" t="n">
-        <v>0.35</v>
-      </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>dual pet feeder</t>
+          <t>quiet cat water fountain</t>
         </is>
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6869,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6886,27 +6882,19 @@
           <t>V2-KeywordTest</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>V2-Test-DualFeeders</t>
-        </is>
-      </c>
       <c r="O161" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="S161" t="n">
-        <v>0.68</v>
-      </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>auto cat feeder</t>
+          <t>small cat water fountain</t>
         </is>
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>negativeExact</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6906,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6936,23 +6924,18 @@
           <t>V2-Test-DualFeeders</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Test - Dual Feeders</t>
+        </is>
+      </c>
       <c r="O162" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="S162" t="n">
+      <c r="R162" t="n">
         <v>0.4</v>
-      </c>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>cat food dispenser</t>
-        </is>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
       </c>
     </row>
     <row r="163">
@@ -6963,7 +6946,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6986,17 +6969,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S163" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="T163" t="inlineStr">
-        <is>
-          <t>automatic dog feeder</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>phrase</t>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>LW-EZAJ-KKZD</t>
         </is>
       </c>
     </row>
@@ -7008,7 +6983,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7031,17 +7006,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S164" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="T164" t="inlineStr">
-        <is>
-          <t>timed pet feeder</t>
-        </is>
-      </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>phrase</t>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>93-E8EG-20UY</t>
         </is>
       </c>
     </row>
@@ -7077,11 +7044,11 @@
         </is>
       </c>
       <c r="S165" t="n">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
-          <t>cat feeder for 2 cats</t>
+          <t>dual cat feeder</t>
         </is>
       </c>
       <c r="U165" t="inlineStr">
@@ -7122,11 +7089,11 @@
         </is>
       </c>
       <c r="S166" t="n">
-        <v>0.68</v>
+        <v>0.35</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
-          <t>automatic cat feeder 2 cats</t>
+          <t>dual pet feeder</t>
         </is>
       </c>
       <c r="U166" t="inlineStr">
@@ -7167,11 +7134,11 @@
         </is>
       </c>
       <c r="S167" t="n">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>automatic cat feeder for two cats</t>
+          <t>auto cat feeder</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
@@ -7216,7 +7183,7 @@
       </c>
       <c r="T168" t="inlineStr">
         <is>
-          <t>automatic feeder for 2 cats</t>
+          <t>cat food dispenser</t>
         </is>
       </c>
       <c r="U168" t="inlineStr">
@@ -7261,7 +7228,7 @@
       </c>
       <c r="T169" t="inlineStr">
         <is>
-          <t>dual automatic cat feeder</t>
+          <t>automatic dog feeder</t>
         </is>
       </c>
       <c r="U169" t="inlineStr">
@@ -7302,11 +7269,11 @@
         </is>
       </c>
       <c r="S170" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
-          <t>dual bowl automatic cat feeder</t>
+          <t>timed pet feeder</t>
         </is>
       </c>
       <c r="U170" t="inlineStr">
@@ -7351,7 +7318,7 @@
       </c>
       <c r="T171" t="inlineStr">
         <is>
-          <t>automatic cat feeder with 2 bowls</t>
+          <t>cat feeder for 2 cats</t>
         </is>
       </c>
       <c r="U171" t="inlineStr">
@@ -7392,11 +7359,11 @@
         </is>
       </c>
       <c r="S172" t="n">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>automatic cat feeder with stainless steel bowls</t>
+          <t>automatic cat feeder 2 cats</t>
         </is>
       </c>
       <c r="U172" t="inlineStr">
@@ -7441,7 +7408,7 @@
       </c>
       <c r="T173" t="inlineStr">
         <is>
-          <t>automatic pet feeder for 2 cats</t>
+          <t>automatic cat feeder for two cats</t>
         </is>
       </c>
       <c r="U173" t="inlineStr">
@@ -7486,7 +7453,7 @@
       </c>
       <c r="T174" t="inlineStr">
         <is>
-          <t>automatic cat feeder dry food</t>
+          <t>automatic feeder for 2 cats</t>
         </is>
       </c>
       <c r="U174" t="inlineStr">
@@ -7531,7 +7498,7 @@
       </c>
       <c r="T175" t="inlineStr">
         <is>
-          <t>cat feeder with timer</t>
+          <t>dual automatic cat feeder</t>
         </is>
       </c>
       <c r="U175" t="inlineStr">
@@ -7576,7 +7543,7 @@
       </c>
       <c r="T176" t="inlineStr">
         <is>
-          <t>automatic cat feeder 2 way audio</t>
+          <t>dual bowl automatic cat feeder</t>
         </is>
       </c>
       <c r="U176" t="inlineStr">
@@ -7621,7 +7588,7 @@
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>quiet automatic cat feeder</t>
+          <t>automatic cat feeder with 2 bowls</t>
         </is>
       </c>
       <c r="U177" t="inlineStr">
@@ -7666,7 +7633,7 @@
       </c>
       <c r="T178" t="inlineStr">
         <is>
-          <t>automatic dog feeder for small dogs</t>
+          <t>automatic cat feeder with stainless steel bowls</t>
         </is>
       </c>
       <c r="U178" t="inlineStr">
@@ -7711,7 +7678,7 @@
       </c>
       <c r="T179" t="inlineStr">
         <is>
-          <t>pet food dispenser automatic</t>
+          <t>automatic pet feeder for 2 cats</t>
         </is>
       </c>
       <c r="U179" t="inlineStr">
@@ -7756,7 +7723,7 @@
       </c>
       <c r="T180" t="inlineStr">
         <is>
-          <t>3l automatic cat feeder</t>
+          <t>automatic cat feeder dry food</t>
         </is>
       </c>
       <c r="U180" t="inlineStr">
@@ -7797,11 +7764,11 @@
         </is>
       </c>
       <c r="S181" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
-          <t>cat feeder automatic</t>
+          <t>cat feeder with timer</t>
         </is>
       </c>
       <c r="U181" t="inlineStr">
@@ -7842,11 +7809,11 @@
         </is>
       </c>
       <c r="S182" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>cat automatic feeders</t>
+          <t>automatic cat feeder 2 way audio</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
@@ -7887,11 +7854,11 @@
         </is>
       </c>
       <c r="S183" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
-          <t>dog feeder automatic</t>
+          <t>quiet automatic cat feeder</t>
         </is>
       </c>
       <c r="U183" t="inlineStr">
@@ -7932,11 +7899,11 @@
         </is>
       </c>
       <c r="S184" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
-          <t>dog automatic feeders</t>
+          <t>automatic dog feeder for small dogs</t>
         </is>
       </c>
       <c r="U184" t="inlineStr">
@@ -7977,11 +7944,11 @@
         </is>
       </c>
       <c r="S185" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
-          <t>auto dog feeder</t>
+          <t>pet food dispenser automatic</t>
         </is>
       </c>
       <c r="U185" t="inlineStr">
@@ -8022,11 +7989,11 @@
         </is>
       </c>
       <c r="S186" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
-          <t>automatic feeder cat dry food</t>
+          <t>3l automatic cat feeder</t>
         </is>
       </c>
       <c r="U186" t="inlineStr">
@@ -8067,11 +8034,11 @@
         </is>
       </c>
       <c r="S187" t="n">
-        <v>0.68</v>
+        <v>0.45</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>auto feeder cat food</t>
+          <t>cat feeder automatic</t>
         </is>
       </c>
       <c r="U187" t="inlineStr">
@@ -8112,11 +8079,11 @@
         </is>
       </c>
       <c r="S188" t="n">
-        <v>0.68</v>
+        <v>0.45</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>cat auto feeder</t>
+          <t>cat automatic feeders</t>
         </is>
       </c>
       <c r="U188" t="inlineStr">
@@ -8161,7 +8128,7 @@
       </c>
       <c r="T189" t="inlineStr">
         <is>
-          <t>dog food dispenser automatic</t>
+          <t>dog feeder automatic</t>
         </is>
       </c>
       <c r="U189" t="inlineStr">
@@ -8206,7 +8173,7 @@
       </c>
       <c r="T190" t="inlineStr">
         <is>
-          <t>pet feeder automatic</t>
+          <t>dog automatic feeders</t>
         </is>
       </c>
       <c r="U190" t="inlineStr">
@@ -8251,7 +8218,7 @@
       </c>
       <c r="T191" t="inlineStr">
         <is>
-          <t>automatic dog food dispenser</t>
+          <t>auto dog feeder</t>
         </is>
       </c>
       <c r="U191" t="inlineStr">
@@ -8296,7 +8263,7 @@
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>automatic food dispenser for cats</t>
+          <t>automatic feeder cat dry food</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
@@ -8341,7 +8308,7 @@
       </c>
       <c r="T193" t="inlineStr">
         <is>
-          <t>timed cat feeders for dry food</t>
+          <t>auto feeder cat food</t>
         </is>
       </c>
       <c r="U193" t="inlineStr">
@@ -8386,7 +8353,7 @@
       </c>
       <c r="T194" t="inlineStr">
         <is>
-          <t>cat food automatic feeder</t>
+          <t>cat auto feeder</t>
         </is>
       </c>
       <c r="U194" t="inlineStr">
@@ -8431,7 +8398,7 @@
       </c>
       <c r="T195" t="inlineStr">
         <is>
-          <t>timed dog feeder</t>
+          <t>dog food dispenser automatic</t>
         </is>
       </c>
       <c r="U195" t="inlineStr">
@@ -8472,11 +8439,11 @@
         </is>
       </c>
       <c r="S196" t="n">
-        <v>0.35</v>
+        <v>0.68</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
-          <t>double cat feeder</t>
+          <t>pet feeder automatic</t>
         </is>
       </c>
       <c r="U196" t="inlineStr">
@@ -8521,7 +8488,7 @@
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>auto pet feeder</t>
+          <t>automatic dog food dispenser</t>
         </is>
       </c>
       <c r="U197" t="inlineStr">
@@ -8566,7 +8533,7 @@
       </c>
       <c r="T198" t="inlineStr">
         <is>
-          <t>auto feeder dog food</t>
+          <t>automatic food dispenser for cats</t>
         </is>
       </c>
       <c r="U198" t="inlineStr">
@@ -8611,7 +8578,7 @@
       </c>
       <c r="T199" t="inlineStr">
         <is>
-          <t>automatic cat feeder programmable</t>
+          <t>timed cat feeders for dry food</t>
         </is>
       </c>
       <c r="U199" t="inlineStr">
@@ -8656,7 +8623,7 @@
       </c>
       <c r="T200" t="inlineStr">
         <is>
-          <t>automatic feeder dog dry food</t>
+          <t>cat food automatic feeder</t>
         </is>
       </c>
       <c r="U200" t="inlineStr">
@@ -8701,7 +8668,7 @@
       </c>
       <c r="T201" t="inlineStr">
         <is>
-          <t>double automatic cat feeder</t>
+          <t>timed dog feeder</t>
         </is>
       </c>
       <c r="U201" t="inlineStr">
@@ -8742,11 +8709,11 @@
         </is>
       </c>
       <c r="S202" t="n">
-        <v>0.68</v>
+        <v>0.35</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>dog food automatic feeder</t>
+          <t>double cat feeder</t>
         </is>
       </c>
       <c r="U202" t="inlineStr">
@@ -8791,7 +8758,7 @@
       </c>
       <c r="T203" t="inlineStr">
         <is>
-          <t>automatic food dispenser for dogs</t>
+          <t>auto pet feeder</t>
         </is>
       </c>
       <c r="U203" t="inlineStr">
@@ -8836,7 +8803,7 @@
       </c>
       <c r="T204" t="inlineStr">
         <is>
-          <t>timed feeder for cats</t>
+          <t>auto feeder dog food</t>
         </is>
       </c>
       <c r="U204" t="inlineStr">
@@ -8881,7 +8848,7 @@
       </c>
       <c r="T205" t="inlineStr">
         <is>
-          <t>automatic pet feeder for dogs</t>
+          <t>automatic cat feeder programmable</t>
         </is>
       </c>
       <c r="U205" t="inlineStr">
@@ -8926,7 +8893,7 @@
       </c>
       <c r="T206" t="inlineStr">
         <is>
-          <t>2 cat automatic feeder</t>
+          <t>automatic feeder dog dry food</t>
         </is>
       </c>
       <c r="U206" t="inlineStr">
@@ -8971,7 +8938,7 @@
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>two cat automatic feeder</t>
+          <t>double automatic cat feeder</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
@@ -9016,7 +8983,7 @@
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t>timed dog food dispenser</t>
+          <t>dog food automatic feeder</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
@@ -9061,7 +9028,7 @@
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>autofeeder cat food</t>
+          <t>automatic food dispenser for dogs</t>
         </is>
       </c>
       <c r="U209" t="inlineStr">
@@ -9078,7 +9045,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9093,12 +9060,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>V2-Test-WiFiFeeder</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>Test - WiFi Feeder</t>
+          <t>V2-Test-DualFeeders</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -9106,8 +9068,18 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="R210" t="n">
-        <v>0.2</v>
+      <c r="S210" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>timed feeder for cats</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
       </c>
     </row>
     <row r="211">
@@ -9118,7 +9090,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9133,7 +9105,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>V2-Test-WiFiFeeder</t>
+          <t>V2-Test-DualFeeders</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -9141,9 +9113,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q211" t="inlineStr">
-        <is>
-          <t>QO-7VBS-CVT4</t>
+      <c r="S211" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>automatic pet feeder for dogs</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9150,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>V2-Test-WiFiFeeder</t>
+          <t>V2-Test-DualFeeders</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -9179,11 +9159,11 @@
         </is>
       </c>
       <c r="S212" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>wifi automatic cat feeder</t>
+          <t>2 cat automatic feeder</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
@@ -9215,7 +9195,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>V2-Test-WiFiFeeder</t>
+          <t>V2-Test-DualFeeders</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -9224,11 +9204,11 @@
         </is>
       </c>
       <c r="S213" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
-          <t>smart automatic cat feeder</t>
+          <t>two cat automatic feeder</t>
         </is>
       </c>
       <c r="U213" t="inlineStr">
@@ -9260,7 +9240,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>V2-Test-WiFiFeeder</t>
+          <t>V2-Test-DualFeeders</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -9269,11 +9249,11 @@
         </is>
       </c>
       <c r="S214" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>wifi cat feeder for 2 cats</t>
+          <t>timed dog food dispenser</t>
         </is>
       </c>
       <c r="U214" t="inlineStr">
@@ -9305,7 +9285,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>V2-Test-WiFiFeeder</t>
+          <t>V2-Test-DualFeeders</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -9314,11 +9294,11 @@
         </is>
       </c>
       <c r="S215" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
-          <t>wifi automatic dog feeder</t>
+          <t>autofeeder cat food</t>
         </is>
       </c>
       <c r="U215" t="inlineStr">
@@ -9335,7 +9315,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9353,23 +9333,18 @@
           <t>V2-Test-WiFiFeeder</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Test - WiFi Feeder</t>
+        </is>
+      </c>
       <c r="O216" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="S216" t="n">
+      <c r="R216" t="n">
         <v>0.2</v>
-      </c>
-      <c r="T216" t="inlineStr">
-        <is>
-          <t>automatic pet feeder wifi</t>
-        </is>
-      </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
       </c>
     </row>
     <row r="217">
@@ -9380,7 +9355,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -9403,17 +9378,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S217" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T217" t="inlineStr">
-        <is>
-          <t>cat feeder app control</t>
-        </is>
-      </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>phrase</t>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>QO-7VBS-CVT4</t>
         </is>
       </c>
     </row>
@@ -9453,7 +9420,7 @@
       </c>
       <c r="T218" t="inlineStr">
         <is>
-          <t>pet feeder with app</t>
+          <t>wifi automatic cat feeder</t>
         </is>
       </c>
       <c r="U218" t="inlineStr">
@@ -9498,7 +9465,7 @@
       </c>
       <c r="T219" t="inlineStr">
         <is>
-          <t>cat feeder with voice recorder</t>
+          <t>smart automatic cat feeder</t>
         </is>
       </c>
       <c r="U219" t="inlineStr">
@@ -9543,7 +9510,7 @@
       </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t>automatic cat feeder with voice recording</t>
+          <t>wifi cat feeder for 2 cats</t>
         </is>
       </c>
       <c r="U220" t="inlineStr">
@@ -9588,7 +9555,7 @@
       </c>
       <c r="T221" t="inlineStr">
         <is>
-          <t>5l automatic cat feeder</t>
+          <t>wifi automatic dog feeder</t>
         </is>
       </c>
       <c r="U221" t="inlineStr">
@@ -9633,7 +9600,7 @@
       </c>
       <c r="T222" t="inlineStr">
         <is>
-          <t>automatic cat feeder 5l</t>
+          <t>automatic pet feeder wifi</t>
         </is>
       </c>
       <c r="U222" t="inlineStr">
@@ -9678,7 +9645,7 @@
       </c>
       <c r="T223" t="inlineStr">
         <is>
-          <t>large capacity automatic cat feeder</t>
+          <t>cat feeder app control</t>
         </is>
       </c>
       <c r="U223" t="inlineStr">
@@ -9723,7 +9690,7 @@
       </c>
       <c r="T224" t="inlineStr">
         <is>
-          <t>elevated automatic cat feeder</t>
+          <t>pet feeder with app</t>
         </is>
       </c>
       <c r="U224" t="inlineStr">
@@ -9768,7 +9735,7 @@
       </c>
       <c r="T225" t="inlineStr">
         <is>
-          <t>automatic dog feeder wifi</t>
+          <t>cat feeder with voice recorder</t>
         </is>
       </c>
       <c r="U225" t="inlineStr">
@@ -9813,7 +9780,7 @@
       </c>
       <c r="T226" t="inlineStr">
         <is>
-          <t>wifi automatic pet feeder for 2 cats</t>
+          <t>automatic cat feeder with voice recording</t>
         </is>
       </c>
       <c r="U226" t="inlineStr">
@@ -9858,7 +9825,7 @@
       </c>
       <c r="T227" t="inlineStr">
         <is>
-          <t>smart dual bowl cat feeder</t>
+          <t>5l automatic cat feeder</t>
         </is>
       </c>
       <c r="U227" t="inlineStr">
@@ -9903,7 +9870,7 @@
       </c>
       <c r="T228" t="inlineStr">
         <is>
-          <t>large capacity automatic dog feeder</t>
+          <t>automatic cat feeder 5l</t>
         </is>
       </c>
       <c r="U228" t="inlineStr">
@@ -9948,7 +9915,7 @@
       </c>
       <c r="T229" t="inlineStr">
         <is>
-          <t>cat feeder with app</t>
+          <t>large capacity automatic cat feeder</t>
         </is>
       </c>
       <c r="U229" t="inlineStr">
@@ -9993,7 +9960,7 @@
       </c>
       <c r="T230" t="inlineStr">
         <is>
-          <t>elevated automatic dog feeder</t>
+          <t>elevated automatic cat feeder</t>
         </is>
       </c>
       <c r="U230" t="inlineStr">
@@ -10010,7 +9977,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -10025,12 +9992,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>V2-Test-CameraFeeder</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>Test - Camera Feeder</t>
+          <t>V2-Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -10038,8 +10000,18 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="R231" t="n">
-        <v>0.4</v>
+      <c r="S231" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>automatic dog feeder wifi</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -10050,7 +10022,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -10065,7 +10037,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>V2-Test-CameraFeeder</t>
+          <t>V2-Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -10073,9 +10045,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q232" t="inlineStr">
-        <is>
-          <t>2H-2T1T-CJC3</t>
+      <c r="S232" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>wifi automatic pet feeder for 2 cats</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10082,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>V2-Test-CameraFeeder</t>
+          <t>V2-Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -10111,11 +10091,11 @@
         </is>
       </c>
       <c r="S233" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
-          <t>camera cat feeder</t>
+          <t>smart dual bowl cat feeder</t>
         </is>
       </c>
       <c r="U233" t="inlineStr">
@@ -10147,7 +10127,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>V2-Test-CameraFeeder</t>
+          <t>V2-Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -10156,11 +10136,11 @@
         </is>
       </c>
       <c r="S234" t="n">
-        <v>0.55</v>
+        <v>0.2</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
-          <t>camera pet feeder</t>
+          <t>large capacity automatic dog feeder</t>
         </is>
       </c>
       <c r="U234" t="inlineStr">
@@ -10192,7 +10172,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>V2-Test-CameraFeeder</t>
+          <t>V2-Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -10201,11 +10181,11 @@
         </is>
       </c>
       <c r="S235" t="n">
-        <v>0.55</v>
+        <v>0.2</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>camera dog feeder</t>
+          <t>cat feeder with app</t>
         </is>
       </c>
       <c r="U235" t="inlineStr">
@@ -10237,7 +10217,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>V2-Test-CameraFeeder</t>
+          <t>V2-Test-WiFiFeeder</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -10246,11 +10226,11 @@
         </is>
       </c>
       <c r="S236" t="n">
-        <v>0.55</v>
+        <v>0.2</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
-          <t>pet camera feeder</t>
+          <t>elevated automatic dog feeder</t>
         </is>
       </c>
       <c r="U236" t="inlineStr">
@@ -10267,7 +10247,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -10285,23 +10265,18 @@
           <t>V2-Test-CameraFeeder</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Test - Camera Feeder</t>
+        </is>
+      </c>
       <c r="O237" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="S237" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="T237" t="inlineStr">
-        <is>
-          <t>dog feeder with camera</t>
-        </is>
-      </c>
-      <c r="U237" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
+      <c r="R237" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="238">
@@ -10312,7 +10287,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -10335,17 +10310,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S238" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="T238" t="inlineStr">
-        <is>
-          <t>automatic pet feeder with camera</t>
-        </is>
-      </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>phrase</t>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>2H-2T1T-CJC3</t>
         </is>
       </c>
     </row>
@@ -10381,11 +10348,11 @@
         </is>
       </c>
       <c r="S239" t="n">
-        <v>0.74</v>
+        <v>0.35</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t>cat food dispenser with camera</t>
+          <t>camera cat feeder</t>
         </is>
       </c>
       <c r="U239" t="inlineStr">
@@ -10426,11 +10393,11 @@
         </is>
       </c>
       <c r="S240" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>dog food dispenser with camera</t>
+          <t>camera pet feeder</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
@@ -10471,11 +10438,11 @@
         </is>
       </c>
       <c r="S241" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
-          <t>wifi cat feeder with camera</t>
+          <t>camera dog feeder</t>
         </is>
       </c>
       <c r="U241" t="inlineStr">
@@ -10516,11 +10483,11 @@
         </is>
       </c>
       <c r="S242" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>smart pet feeder with camera</t>
+          <t>pet camera feeder</t>
         </is>
       </c>
       <c r="U242" t="inlineStr">
@@ -10561,11 +10528,11 @@
         </is>
       </c>
       <c r="S243" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>smart cat feeder with camera</t>
+          <t>dog feeder with camera</t>
         </is>
       </c>
       <c r="U243" t="inlineStr">
@@ -10606,11 +10573,11 @@
         </is>
       </c>
       <c r="S244" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>automatic feeder with camera</t>
+          <t>automatic pet feeder with camera</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
@@ -10651,11 +10618,11 @@
         </is>
       </c>
       <c r="S245" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>auto cat feeder with camera</t>
+          <t>cat food dispenser with camera</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
@@ -10700,7 +10667,7 @@
       </c>
       <c r="T246" t="inlineStr">
         <is>
-          <t>automatic cat feeder with camera and audio</t>
+          <t>dog food dispenser with camera</t>
         </is>
       </c>
       <c r="U246" t="inlineStr">
@@ -10745,7 +10712,7 @@
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>cat feeder with camera 2 way audio</t>
+          <t>wifi cat feeder with camera</t>
         </is>
       </c>
       <c r="U247" t="inlineStr">
@@ -10790,7 +10757,7 @@
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>pet feeder camera 2 way audio</t>
+          <t>smart pet feeder with camera</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
@@ -10835,7 +10802,7 @@
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t>pet feeder with camera and app</t>
+          <t>smart cat feeder with camera</t>
         </is>
       </c>
       <c r="U249" t="inlineStr">
@@ -10876,11 +10843,11 @@
         </is>
       </c>
       <c r="S250" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>automatic cat feeder 1080p camera</t>
+          <t>automatic feeder with camera</t>
         </is>
       </c>
       <c r="U250" t="inlineStr">
@@ -10925,7 +10892,7 @@
       </c>
       <c r="T251" t="inlineStr">
         <is>
-          <t>cat feeder with hd camera</t>
+          <t>auto cat feeder with camera</t>
         </is>
       </c>
       <c r="U251" t="inlineStr">
@@ -10970,7 +10937,7 @@
       </c>
       <c r="T252" t="inlineStr">
         <is>
-          <t>automatic cat feeder with video</t>
+          <t>automatic cat feeder with camera and audio</t>
         </is>
       </c>
       <c r="U252" t="inlineStr">
@@ -11015,7 +10982,7 @@
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>camera feeder for cats</t>
+          <t>cat feeder with camera 2 way audio</t>
         </is>
       </c>
       <c r="U253" t="inlineStr">
@@ -11060,7 +11027,7 @@
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>automatic cat feeder with camera wifi</t>
+          <t>pet feeder camera 2 way audio</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
@@ -11105,7 +11072,7 @@
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>cat feeder with camera for small dogs</t>
+          <t>pet feeder with camera and app</t>
         </is>
       </c>
       <c r="U255" t="inlineStr">
@@ -11146,11 +11113,11 @@
         </is>
       </c>
       <c r="S256" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>wifi automatic cat feeder app control</t>
+          <t>automatic cat feeder 1080p camera</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
@@ -11191,11 +11158,11 @@
         </is>
       </c>
       <c r="S257" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>smart cat feeder</t>
+          <t>cat feeder with hd camera</t>
         </is>
       </c>
       <c r="U257" t="inlineStr">
@@ -11236,11 +11203,11 @@
         </is>
       </c>
       <c r="S258" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>smart pet feeder</t>
+          <t>automatic cat feeder with video</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
@@ -11281,11 +11248,11 @@
         </is>
       </c>
       <c r="S259" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
-          <t>smart automatic dog feeder wifi app control</t>
+          <t>camera feeder for cats</t>
         </is>
       </c>
       <c r="U259" t="inlineStr">
@@ -11326,11 +11293,11 @@
         </is>
       </c>
       <c r="S260" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>automatic cat feeder wifi</t>
+          <t>automatic cat feeder with camera wifi</t>
         </is>
       </c>
       <c r="U260" t="inlineStr">
@@ -11371,11 +11338,11 @@
         </is>
       </c>
       <c r="S261" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
-          <t>smart feeder for cats</t>
+          <t>cat feeder with camera for small dogs</t>
         </is>
       </c>
       <c r="U261" t="inlineStr">
@@ -11420,7 +11387,7 @@
       </c>
       <c r="T262" t="inlineStr">
         <is>
-          <t>smart dog feeder</t>
+          <t>wifi automatic cat feeder app control</t>
         </is>
       </c>
       <c r="U262" t="inlineStr">
@@ -11465,7 +11432,7 @@
       </c>
       <c r="T263" t="inlineStr">
         <is>
-          <t>wifi dog feeder</t>
+          <t>smart cat feeder</t>
         </is>
       </c>
       <c r="U263" t="inlineStr">
@@ -11510,7 +11477,7 @@
       </c>
       <c r="T264" t="inlineStr">
         <is>
-          <t>automatic cat feeder with camera 1080p</t>
+          <t>smart pet feeder</t>
         </is>
       </c>
       <c r="U264" t="inlineStr">
@@ -11551,11 +11518,11 @@
         </is>
       </c>
       <c r="S265" t="n">
-        <v>0.35</v>
+        <v>0.74</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
-          <t>wifi cat feeder app control</t>
+          <t>smart automatic dog feeder wifi app control</t>
         </is>
       </c>
       <c r="U265" t="inlineStr">
@@ -11596,11 +11563,11 @@
         </is>
       </c>
       <c r="S266" t="n">
-        <v>0.35</v>
+        <v>0.74</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
-          <t>automatic cat feeder battery backup</t>
+          <t>automatic cat feeder wifi</t>
         </is>
       </c>
       <c r="U266" t="inlineStr">
@@ -11641,11 +11608,11 @@
         </is>
       </c>
       <c r="S267" t="n">
-        <v>0.35</v>
+        <v>0.74</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
-          <t>wi-fi enabled automatic cat feeder with app control</t>
+          <t>smart feeder for cats</t>
         </is>
       </c>
       <c r="U267" t="inlineStr">
@@ -11686,11 +11653,11 @@
         </is>
       </c>
       <c r="S268" t="n">
-        <v>0.35</v>
+        <v>0.74</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
-          <t>automatic dog feeder with wifi</t>
+          <t>smart dog feeder</t>
         </is>
       </c>
       <c r="U268" t="inlineStr">
@@ -11735,7 +11702,7 @@
       </c>
       <c r="T269" t="inlineStr">
         <is>
-          <t>wifi pet feeder</t>
+          <t>wifi dog feeder</t>
         </is>
       </c>
       <c r="U269" t="inlineStr">
@@ -11780,7 +11747,7 @@
       </c>
       <c r="T270" t="inlineStr">
         <is>
-          <t>smart feeder with camera</t>
+          <t>automatic cat feeder with camera 1080p</t>
         </is>
       </c>
       <c r="U270" t="inlineStr">
@@ -11825,7 +11792,7 @@
       </c>
       <c r="T271" t="inlineStr">
         <is>
-          <t>smart cat food dispensers</t>
+          <t>wifi cat feeder app control</t>
         </is>
       </c>
       <c r="U271" t="inlineStr">
@@ -11870,7 +11837,7 @@
       </c>
       <c r="T272" t="inlineStr">
         <is>
-          <t>smart cam feeder</t>
+          <t>automatic cat feeder battery backup</t>
         </is>
       </c>
       <c r="U272" t="inlineStr">
@@ -11911,11 +11878,11 @@
         </is>
       </c>
       <c r="S273" t="n">
-        <v>0.74</v>
+        <v>0.35</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
-          <t>wifi enabled automatic cat feeder</t>
+          <t>wi-fi enabled automatic cat feeder with app control</t>
         </is>
       </c>
       <c r="U273" t="inlineStr">
@@ -11960,7 +11927,7 @@
       </c>
       <c r="T274" t="inlineStr">
         <is>
-          <t>smart petfeeder</t>
+          <t>automatic dog feeder with wifi</t>
         </is>
       </c>
       <c r="U274" t="inlineStr">
@@ -12001,11 +11968,11 @@
         </is>
       </c>
       <c r="S275" t="n">
-        <v>0.35</v>
+        <v>0.74</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>wifi cat food dispenser</t>
+          <t>wifi pet feeder</t>
         </is>
       </c>
       <c r="U275" t="inlineStr">
@@ -12046,11 +12013,11 @@
         </is>
       </c>
       <c r="S276" t="n">
-        <v>0.35</v>
+        <v>0.74</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
-          <t>smart dog food dispenser</t>
+          <t>smart feeder with camera</t>
         </is>
       </c>
       <c r="U276" t="inlineStr">
@@ -12067,7 +12034,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -12082,12 +12049,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>V2-Test-StainlessFountain</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>Test - Stainless Fountain</t>
+          <t>V2-Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
@@ -12095,8 +12057,18 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="R277" t="n">
-        <v>0.4</v>
+      <c r="S277" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>smart cat food dispensers</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
       </c>
     </row>
     <row r="278">
@@ -12107,7 +12079,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -12122,7 +12094,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>V2-Test-StainlessFountain</t>
+          <t>V2-Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
@@ -12130,9 +12102,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q278" t="inlineStr">
-        <is>
-          <t>QY-HHE8-0H1B</t>
+      <c r="S278" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>smart cam feeder</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -12159,7 +12139,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>V2-Test-StainlessFountain</t>
+          <t>V2-Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O279" t="inlineStr">
@@ -12168,11 +12148,11 @@
         </is>
       </c>
       <c r="S279" t="n">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
-          <t>metal pet fountain</t>
+          <t>wifi enabled automatic cat feeder</t>
         </is>
       </c>
       <c r="U279" t="inlineStr">
@@ -12204,7 +12184,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>V2-Test-StainlessFountain</t>
+          <t>V2-Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
@@ -12213,11 +12193,11 @@
         </is>
       </c>
       <c r="S280" t="n">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
-          <t>metal dog fountain</t>
+          <t>smart petfeeder</t>
         </is>
       </c>
       <c r="U280" t="inlineStr">
@@ -12249,7 +12229,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>V2-Test-StainlessFountain</t>
+          <t>V2-Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
@@ -12258,11 +12238,11 @@
         </is>
       </c>
       <c r="S281" t="n">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
-          <t>steel cat fountain</t>
+          <t>wifi cat food dispenser</t>
         </is>
       </c>
       <c r="U281" t="inlineStr">
@@ -12294,7 +12274,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>V2-Test-StainlessFountain</t>
+          <t>V2-Test-CameraFeeder</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
@@ -12303,11 +12283,11 @@
         </is>
       </c>
       <c r="S282" t="n">
-        <v>0.8</v>
+        <v>0.35</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
-          <t>stainless steel dog water fountain</t>
+          <t>smart dog food dispenser</t>
         </is>
       </c>
       <c r="U282" t="inlineStr">
@@ -12324,7 +12304,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -12342,23 +12322,18 @@
           <t>V2-Test-StainlessFountain</t>
         </is>
       </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Test - Stainless Fountain</t>
+        </is>
+      </c>
       <c r="O283" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="S283" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="T283" t="inlineStr">
-        <is>
-          <t>stainless steel pet water fountain</t>
-        </is>
-      </c>
-      <c r="U283" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
+      <c r="R283" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="284">
@@ -12369,7 +12344,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -12392,17 +12367,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S284" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="T284" t="inlineStr">
-        <is>
-          <t>stainless steel pet fountain</t>
-        </is>
-      </c>
-      <c r="U284" t="inlineStr">
-        <is>
-          <t>phrase</t>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>QY-HHE8-0H1B</t>
         </is>
       </c>
     </row>
@@ -12438,11 +12405,11 @@
         </is>
       </c>
       <c r="S285" t="n">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
-          <t>stainless steel cat fountain</t>
+          <t>metal pet fountain</t>
         </is>
       </c>
       <c r="U285" t="inlineStr">
@@ -12483,11 +12450,11 @@
         </is>
       </c>
       <c r="S286" t="n">
-        <v>0.77</v>
+        <v>0.55</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
-          <t>dog water fountain stainless steel</t>
+          <t>metal dog fountain</t>
         </is>
       </c>
       <c r="U286" t="inlineStr">
@@ -12528,11 +12495,11 @@
         </is>
       </c>
       <c r="S287" t="n">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
-          <t>pet water fountain stainless steel</t>
+          <t>steel cat fountain</t>
         </is>
       </c>
       <c r="U287" t="inlineStr">
@@ -12573,11 +12540,11 @@
         </is>
       </c>
       <c r="S288" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
-          <t>stainless steel water fountain for cats</t>
+          <t>stainless steel dog water fountain</t>
         </is>
       </c>
       <c r="U288" t="inlineStr">
@@ -12622,7 +12589,7 @@
       </c>
       <c r="T289" t="inlineStr">
         <is>
-          <t>stainless steel water fountain for dogs</t>
+          <t>stainless steel pet water fountain</t>
         </is>
       </c>
       <c r="U289" t="inlineStr">
@@ -12663,11 +12630,11 @@
         </is>
       </c>
       <c r="S290" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
-          <t>metal dog water fountain</t>
+          <t>stainless steel pet fountain</t>
         </is>
       </c>
       <c r="U290" t="inlineStr">
@@ -12708,11 +12675,11 @@
         </is>
       </c>
       <c r="S291" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="T291" t="inlineStr">
         <is>
-          <t>metal pet water fountain</t>
+          <t>stainless steel cat fountain</t>
         </is>
       </c>
       <c r="U291" t="inlineStr">
@@ -12753,11 +12720,11 @@
         </is>
       </c>
       <c r="S292" t="n">
-        <v>0.4</v>
+        <v>0.77</v>
       </c>
       <c r="T292" t="inlineStr">
         <is>
-          <t>108oz cat water fountain</t>
+          <t>dog water fountain stainless steel</t>
         </is>
       </c>
       <c r="U292" t="inlineStr">
@@ -12798,11 +12765,11 @@
         </is>
       </c>
       <c r="S293" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="T293" t="inlineStr">
         <is>
-          <t>3.2l cat water fountain</t>
+          <t>pet water fountain stainless steel</t>
         </is>
       </c>
       <c r="U293" t="inlineStr">
@@ -12843,11 +12810,11 @@
         </is>
       </c>
       <c r="S294" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
-          <t>108 oz pet water fountain</t>
+          <t>stainless steel water fountain for cats</t>
         </is>
       </c>
       <c r="U294" t="inlineStr">
@@ -12888,11 +12855,11 @@
         </is>
       </c>
       <c r="S295" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
-          <t>large cat water fountain stainless steel</t>
+          <t>stainless steel water fountain for dogs</t>
         </is>
       </c>
       <c r="U295" t="inlineStr">
@@ -12937,7 +12904,7 @@
       </c>
       <c r="T296" t="inlineStr">
         <is>
-          <t>cat water fountain with led light</t>
+          <t>metal dog water fountain</t>
         </is>
       </c>
       <c r="U296" t="inlineStr">
@@ -12982,7 +12949,7 @@
       </c>
       <c r="T297" t="inlineStr">
         <is>
-          <t>pet water fountain with led light</t>
+          <t>metal pet water fountain</t>
         </is>
       </c>
       <c r="U297" t="inlineStr">
@@ -13027,7 +12994,7 @@
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>faucet cat water fountain</t>
+          <t>108oz cat water fountain</t>
         </is>
       </c>
       <c r="U298" t="inlineStr">
@@ -13072,7 +13039,7 @@
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>cat water fountain dishwasher safe</t>
+          <t>3.2l cat water fountain</t>
         </is>
       </c>
       <c r="U299" t="inlineStr">
@@ -13117,7 +13084,7 @@
       </c>
       <c r="T300" t="inlineStr">
         <is>
-          <t>cat water fountain for multiple cats</t>
+          <t>108 oz pet water fountain</t>
         </is>
       </c>
       <c r="U300" t="inlineStr">
@@ -13162,7 +13129,7 @@
       </c>
       <c r="T301" t="inlineStr">
         <is>
-          <t>quiet stainless steel cat water fountain</t>
+          <t>large cat water fountain stainless steel</t>
         </is>
       </c>
       <c r="U301" t="inlineStr">
@@ -13207,7 +13174,7 @@
       </c>
       <c r="T302" t="inlineStr">
         <is>
-          <t>large capacity cat water fountain</t>
+          <t>cat water fountain with led light</t>
         </is>
       </c>
       <c r="U302" t="inlineStr">
@@ -13248,11 +13215,11 @@
         </is>
       </c>
       <c r="S303" t="n">
-        <v>0.83</v>
+        <v>0.4</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
-          <t>dog water fountain for small dogs</t>
+          <t>pet water fountain with led light</t>
         </is>
       </c>
       <c r="U303" t="inlineStr">
@@ -13297,7 +13264,7 @@
       </c>
       <c r="T304" t="inlineStr">
         <is>
-          <t>water fountains for cats indoor</t>
+          <t>faucet cat water fountain</t>
         </is>
       </c>
       <c r="U304" t="inlineStr">
@@ -13338,11 +13305,11 @@
         </is>
       </c>
       <c r="S305" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
-          <t>cat fountain stainless steel</t>
+          <t>cat water fountain dishwasher safe</t>
         </is>
       </c>
       <c r="U305" t="inlineStr">
@@ -13387,7 +13354,7 @@
       </c>
       <c r="T306" t="inlineStr">
         <is>
-          <t>cat fountains</t>
+          <t>cat water fountain for multiple cats</t>
         </is>
       </c>
       <c r="U306" t="inlineStr">
@@ -13432,7 +13399,7 @@
       </c>
       <c r="T307" t="inlineStr">
         <is>
-          <t>water fountain for dogs</t>
+          <t>quiet stainless steel cat water fountain</t>
         </is>
       </c>
       <c r="U307" t="inlineStr">
@@ -13473,11 +13440,11 @@
         </is>
       </c>
       <c r="S308" t="n">
-        <v>0.83</v>
+        <v>0.4</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
-          <t>dog fountain stainless steel</t>
+          <t>large capacity cat water fountain</t>
         </is>
       </c>
       <c r="U308" t="inlineStr">
@@ -13522,7 +13489,7 @@
       </c>
       <c r="T309" t="inlineStr">
         <is>
-          <t>cat stainless steel water fountain</t>
+          <t>dog water fountain for small dogs</t>
         </is>
       </c>
       <c r="U309" t="inlineStr">
@@ -13563,11 +13530,11 @@
         </is>
       </c>
       <c r="S310" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
-          <t>dog drinking fountain</t>
+          <t>water fountains for cats indoor</t>
         </is>
       </c>
       <c r="U310" t="inlineStr">
@@ -13608,11 +13575,11 @@
         </is>
       </c>
       <c r="S311" t="n">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
-          <t>cat drinking fountain stainless steel</t>
+          <t>cat fountain stainless steel</t>
         </is>
       </c>
       <c r="U311" t="inlineStr">
@@ -13653,11 +13620,11 @@
         </is>
       </c>
       <c r="S312" t="n">
-        <v>0.83</v>
+        <v>0.4</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
-          <t>stainless cat water fountain</t>
+          <t>cat fountains</t>
         </is>
       </c>
       <c r="U312" t="inlineStr">
@@ -13698,11 +13665,11 @@
         </is>
       </c>
       <c r="S313" t="n">
-        <v>0.83</v>
+        <v>0.4</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
-          <t>metal water fountain for cats</t>
+          <t>water fountain for dogs</t>
         </is>
       </c>
       <c r="U313" t="inlineStr">
@@ -13747,7 +13714,7 @@
       </c>
       <c r="T314" t="inlineStr">
         <is>
-          <t>metal cat fountain</t>
+          <t>dog fountain stainless steel</t>
         </is>
       </c>
       <c r="U314" t="inlineStr">
@@ -13788,11 +13755,11 @@
         </is>
       </c>
       <c r="S315" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>
-          <t>large capacity dog water fountain</t>
+          <t>cat stainless steel water fountain</t>
         </is>
       </c>
       <c r="U315" t="inlineStr">
@@ -13833,11 +13800,11 @@
         </is>
       </c>
       <c r="S316" t="n">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="T316" t="inlineStr">
         <is>
-          <t>large capacity pet water fountain</t>
+          <t>dog drinking fountain</t>
         </is>
       </c>
       <c r="U316" t="inlineStr">
@@ -13882,7 +13849,7 @@
       </c>
       <c r="T317" t="inlineStr">
         <is>
-          <t>cat water fountain with led indicator</t>
+          <t>cat drinking fountain stainless steel</t>
         </is>
       </c>
       <c r="U317" t="inlineStr">
@@ -13923,11 +13890,11 @@
         </is>
       </c>
       <c r="S318" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
-          <t>cat waterer</t>
+          <t>stainless cat water fountain</t>
         </is>
       </c>
       <c r="U318" t="inlineStr">
@@ -13968,11 +13935,11 @@
         </is>
       </c>
       <c r="S319" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
-          <t>large pet water fountain</t>
+          <t>metal water fountain for cats</t>
         </is>
       </c>
       <c r="U319" t="inlineStr">
@@ -14017,7 +13984,7 @@
       </c>
       <c r="T320" t="inlineStr">
         <is>
-          <t>easy to clean cat water fountain</t>
+          <t>metal cat fountain</t>
         </is>
       </c>
       <c r="U320" t="inlineStr">
@@ -14058,11 +14025,11 @@
         </is>
       </c>
       <c r="S321" t="n">
-        <v>0.83</v>
+        <v>0.4</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
-          <t>dishwasher safe cat water fountain</t>
+          <t>large capacity dog water fountain</t>
         </is>
       </c>
       <c r="U321" t="inlineStr">
@@ -14103,11 +14070,11 @@
         </is>
       </c>
       <c r="S322" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
-          <t>steel cat water fountain</t>
+          <t>large capacity pet water fountain</t>
         </is>
       </c>
       <c r="U322" t="inlineStr">
@@ -14124,7 +14091,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -14139,12 +14106,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>V2-Test-BasicFountains</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t>Test - Basic Fountains</t>
+          <t>V2-Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
@@ -14152,8 +14114,18 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="R323" t="n">
-        <v>0.2</v>
+      <c r="S323" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>cat water fountain with led indicator</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
       </c>
     </row>
     <row r="324">
@@ -14164,7 +14136,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -14179,7 +14151,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>V2-Test-BasicFountains</t>
+          <t>V2-Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
@@ -14187,14 +14159,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S324" t="n">
+        <v>0.5</v>
+      </c>
       <c r="T324" t="inlineStr">
         <is>
-          <t>battery</t>
+          <t>cat waterer</t>
         </is>
       </c>
       <c r="U324" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -14206,7 +14181,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -14221,7 +14196,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>V2-Test-BasicFountains</t>
+          <t>V2-Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
@@ -14229,9 +14204,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q325" t="inlineStr">
-        <is>
-          <t>L6-L3S1-I7Q6</t>
+      <c r="S325" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>large pet water fountain</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14226,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -14258,7 +14241,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>V2-Test-BasicFountains</t>
+          <t>V2-Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O326" t="inlineStr">
@@ -14266,9 +14249,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q326" t="inlineStr">
-        <is>
-          <t>SD-85ET-IOZ3</t>
+      <c r="S326" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>easy to clean cat water fountain</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -14280,7 +14271,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -14295,7 +14286,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>V2-Test-BasicFountains</t>
+          <t>V2-Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
@@ -14303,9 +14294,17 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q327" t="inlineStr">
-        <is>
-          <t>JE-LQEW-9EHL</t>
+      <c r="S327" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>dishwasher safe cat water fountain</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -14332,7 +14331,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>V2-Test-BasicFountains</t>
+          <t>V2-Test-StainlessFountain</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
@@ -14341,11 +14340,11 @@
         </is>
       </c>
       <c r="S328" t="n">
-        <v>0.2</v>
+        <v>0.83</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
-          <t>pet fountain</t>
+          <t>steel cat water fountain</t>
         </is>
       </c>
       <c r="U328" t="inlineStr">
@@ -14362,7 +14361,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -14380,23 +14379,18 @@
           <t>V2-Test-BasicFountains</t>
         </is>
       </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Test - Basic Fountains</t>
+        </is>
+      </c>
       <c r="O329" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="S329" t="n">
+      <c r="R329" t="n">
         <v>0.2</v>
-      </c>
-      <c r="T329" t="inlineStr">
-        <is>
-          <t>cat water dispenser</t>
-        </is>
-      </c>
-      <c r="U329" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
       </c>
     </row>
     <row r="330">
@@ -14407,7 +14401,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Negative Keyword</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -14430,17 +14424,14 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S330" t="n">
-        <v>0.2</v>
-      </c>
       <c r="T330" t="inlineStr">
         <is>
-          <t>cat drinking fountain</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="U330" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -14452,7 +14443,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -14475,17 +14466,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S331" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T331" t="inlineStr">
-        <is>
-          <t>pet water dispenser</t>
-        </is>
-      </c>
-      <c r="U331" t="inlineStr">
-        <is>
-          <t>phrase</t>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>L6-L3S1-I7Q6</t>
         </is>
       </c>
     </row>
@@ -14497,7 +14480,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -14520,17 +14503,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S332" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T332" t="inlineStr">
-        <is>
-          <t>kitty water fountain</t>
-        </is>
-      </c>
-      <c r="U332" t="inlineStr">
-        <is>
-          <t>phrase</t>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>SD-85ET-IOZ3</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14517,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -14565,17 +14540,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S333" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T333" t="inlineStr">
-        <is>
-          <t>pet drinking fountain</t>
-        </is>
-      </c>
-      <c r="U333" t="inlineStr">
-        <is>
-          <t>phrase</t>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>JE-LQEW-9EHL</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14582,7 @@
       </c>
       <c r="T334" t="inlineStr">
         <is>
-          <t>quiet cat water fountain</t>
+          <t>pet fountain</t>
         </is>
       </c>
       <c r="U334" t="inlineStr">
@@ -14660,7 +14627,7 @@
       </c>
       <c r="T335" t="inlineStr">
         <is>
-          <t>cat water fountain quiet</t>
+          <t>cat water dispenser</t>
         </is>
       </c>
       <c r="U335" t="inlineStr">
@@ -14705,7 +14672,7 @@
       </c>
       <c r="T336" t="inlineStr">
         <is>
-          <t>silent cat water fountain</t>
+          <t>cat drinking fountain</t>
         </is>
       </c>
       <c r="U336" t="inlineStr">
@@ -14750,7 +14717,7 @@
       </c>
       <c r="T337" t="inlineStr">
         <is>
-          <t>pet water fountain for cats</t>
+          <t>pet water dispenser</t>
         </is>
       </c>
       <c r="U337" t="inlineStr">
@@ -14795,7 +14762,7 @@
       </c>
       <c r="T338" t="inlineStr">
         <is>
-          <t>cat water fountain for indoor cats</t>
+          <t>kitty water fountain</t>
         </is>
       </c>
       <c r="U338" t="inlineStr">
@@ -14840,7 +14807,7 @@
       </c>
       <c r="T339" t="inlineStr">
         <is>
-          <t>water fountain for cats indoor</t>
+          <t>pet drinking fountain</t>
         </is>
       </c>
       <c r="U339" t="inlineStr">
@@ -14885,7 +14852,7 @@
       </c>
       <c r="T340" t="inlineStr">
         <is>
-          <t>plastic cat water fountain</t>
+          <t>quiet cat water fountain</t>
         </is>
       </c>
       <c r="U340" t="inlineStr">
@@ -14930,7 +14897,7 @@
       </c>
       <c r="T341" t="inlineStr">
         <is>
-          <t>cat water fountain with water level window</t>
+          <t>cat water fountain quiet</t>
         </is>
       </c>
       <c r="U341" t="inlineStr">
@@ -14975,7 +14942,7 @@
       </c>
       <c r="T342" t="inlineStr">
         <is>
-          <t>pet water fountain for small dogs</t>
+          <t>silent cat water fountain</t>
         </is>
       </c>
       <c r="U342" t="inlineStr">
@@ -15020,7 +14987,7 @@
       </c>
       <c r="T343" t="inlineStr">
         <is>
-          <t>kitten water fountain</t>
+          <t>pet water fountain for cats</t>
         </is>
       </c>
       <c r="U343" t="inlineStr">
@@ -15065,7 +15032,7 @@
       </c>
       <c r="T344" t="inlineStr">
         <is>
-          <t>water bowl fountain for cats</t>
+          <t>cat water fountain for indoor cats</t>
         </is>
       </c>
       <c r="U344" t="inlineStr">
@@ -15110,7 +15077,7 @@
       </c>
       <c r="T345" t="inlineStr">
         <is>
-          <t>small dog water fountain</t>
+          <t>water fountain for cats indoor</t>
         </is>
       </c>
       <c r="U345" t="inlineStr">
@@ -15155,7 +15122,7 @@
       </c>
       <c r="T346" t="inlineStr">
         <is>
-          <t>water dispenser for cats</t>
+          <t>plastic cat water fountain</t>
         </is>
       </c>
       <c r="U346" t="inlineStr">
@@ -15200,7 +15167,7 @@
       </c>
       <c r="T347" t="inlineStr">
         <is>
-          <t>kitty fountain</t>
+          <t>cat water fountain with water level window</t>
         </is>
       </c>
       <c r="U347" t="inlineStr">
@@ -15245,7 +15212,7 @@
       </c>
       <c r="T348" t="inlineStr">
         <is>
-          <t>quiet pet water fountain</t>
+          <t>pet water fountain for small dogs</t>
         </is>
       </c>
       <c r="U348" t="inlineStr">
@@ -15290,7 +15257,7 @@
       </c>
       <c r="T349" t="inlineStr">
         <is>
-          <t>small pet water fountain</t>
+          <t>kitten water fountain</t>
         </is>
       </c>
       <c r="U349" t="inlineStr">
@@ -15335,7 +15302,7 @@
       </c>
       <c r="T350" t="inlineStr">
         <is>
-          <t>small water fountain for cats</t>
+          <t>water bowl fountain for cats</t>
         </is>
       </c>
       <c r="U350" t="inlineStr">
@@ -15380,7 +15347,7 @@
       </c>
       <c r="T351" t="inlineStr">
         <is>
-          <t>kitten fountain</t>
+          <t>small dog water fountain</t>
         </is>
       </c>
       <c r="U351" t="inlineStr">
@@ -15425,7 +15392,7 @@
       </c>
       <c r="T352" t="inlineStr">
         <is>
-          <t>water fountain for small dogs</t>
+          <t>water dispenser for cats</t>
         </is>
       </c>
       <c r="U352" t="inlineStr">
@@ -15442,7 +15409,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -15452,35 +15419,30 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>V2-Discovery</t>
-        </is>
-      </c>
-      <c r="J353" t="inlineStr">
-        <is>
-          <t>PETME2 | Discovery | Auto</t>
-        </is>
-      </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t>20261004</t>
-        </is>
-      </c>
-      <c r="N353" t="inlineStr">
-        <is>
-          <t>Auto</t>
+          <t>V2-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>V2-Test-BasicFountains</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>paused</t>
-        </is>
-      </c>
-      <c r="P353" t="n">
-        <v>5</v>
-      </c>
-      <c r="V353" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S353" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>kitty fountain</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -15492,7 +15454,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -15502,7 +15464,12 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>V2-Discovery</t>
+          <t>V2-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>V2-Test-BasicFountains</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
@@ -15510,14 +15477,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S354" t="n">
+        <v>0.2</v>
+      </c>
       <c r="T354" t="inlineStr">
         <is>
-          <t>replacement</t>
+          <t>quiet pet water fountain</t>
         </is>
       </c>
       <c r="U354" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -15529,7 +15499,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -15539,7 +15509,12 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>V2-Discovery</t>
+          <t>V2-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>V2-Test-BasicFountains</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
@@ -15547,14 +15522,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S355" t="n">
+        <v>0.2</v>
+      </c>
       <c r="T355" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>small pet water fountain</t>
         </is>
       </c>
       <c r="U355" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -15566,7 +15544,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -15576,7 +15554,12 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>V2-Discovery</t>
+          <t>V2-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>V2-Test-BasicFountains</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
@@ -15584,14 +15567,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S356" t="n">
+        <v>0.2</v>
+      </c>
       <c r="T356" t="inlineStr">
         <is>
-          <t>bird</t>
+          <t>small water fountain for cats</t>
         </is>
       </c>
       <c r="U356" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15589,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -15613,7 +15599,12 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>V2-Discovery</t>
+          <t>V2-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>V2-Test-BasicFountains</t>
         </is>
       </c>
       <c r="O357" t="inlineStr">
@@ -15621,14 +15612,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S357" t="n">
+        <v>0.2</v>
+      </c>
       <c r="T357" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>kitten fountain</t>
         </is>
       </c>
       <c r="U357" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -15640,7 +15634,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -15650,7 +15644,12 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>V2-Discovery</t>
+          <t>V2-KeywordTest</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>V2-Test-BasicFountains</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
@@ -15658,14 +15657,17 @@
           <t>enabled</t>
         </is>
       </c>
+      <c r="S358" t="n">
+        <v>0.2</v>
+      </c>
       <c r="T358" t="inlineStr">
         <is>
-          <t>slow feeder</t>
+          <t>water fountain for small dogs</t>
         </is>
       </c>
       <c r="U358" t="inlineStr">
         <is>
-          <t>negativePhrase</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
@@ -15677,7 +15679,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Campaign Negative Keyword</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -15690,19 +15692,32 @@
           <t>V2-Discovery</t>
         </is>
       </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>PETME2 | Discovery | Auto</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>20261004</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="T359" t="inlineStr">
-        <is>
-          <t>petme2</t>
-        </is>
-      </c>
-      <c r="U359" t="inlineStr">
-        <is>
-          <t>negativePhrase</t>
+          <t>paused</t>
+        </is>
+      </c>
+      <c r="P359" t="n">
+        <v>5</v>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15749,7 @@
       </c>
       <c r="T360" t="inlineStr">
         <is>
-          <t>gravity</t>
+          <t>replacement</t>
         </is>
       </c>
       <c r="U360" t="inlineStr">
@@ -15771,7 +15786,7 @@
       </c>
       <c r="T361" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="U361" t="inlineStr">
@@ -15808,7 +15823,7 @@
       </c>
       <c r="T362" t="inlineStr">
         <is>
-          <t>wireless</t>
+          <t>bird</t>
         </is>
       </c>
       <c r="U362" t="inlineStr">
@@ -15845,7 +15860,7 @@
       </c>
       <c r="T363" t="inlineStr">
         <is>
-          <t>ceramic</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="U363" t="inlineStr">
@@ -15882,7 +15897,7 @@
       </c>
       <c r="T364" t="inlineStr">
         <is>
-          <t>outdoor</t>
+          <t>slow feeder</t>
         </is>
       </c>
       <c r="U364" t="inlineStr">
@@ -15919,7 +15934,7 @@
       </c>
       <c r="T365" t="inlineStr">
         <is>
-          <t>heated</t>
+          <t>petme2</t>
         </is>
       </c>
       <c r="U365" t="inlineStr">
@@ -15956,7 +15971,7 @@
       </c>
       <c r="T366" t="inlineStr">
         <is>
-          <t>large dog</t>
+          <t>gravity</t>
         </is>
       </c>
       <c r="U366" t="inlineStr">
@@ -15993,7 +16008,7 @@
       </c>
       <c r="T367" t="inlineStr">
         <is>
-          <t>wet food</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="U367" t="inlineStr">
@@ -16030,12 +16045,12 @@
       </c>
       <c r="T368" t="inlineStr">
         <is>
-          <t>automatic cat feeder</t>
+          <t>wireless</t>
         </is>
       </c>
       <c r="U368" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -16067,12 +16082,12 @@
       </c>
       <c r="T369" t="inlineStr">
         <is>
-          <t>cat feeder automatic</t>
+          <t>ceramic</t>
         </is>
       </c>
       <c r="U369" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -16104,12 +16119,12 @@
       </c>
       <c r="T370" t="inlineStr">
         <is>
-          <t>cat automatic feeders</t>
+          <t>outdoor</t>
         </is>
       </c>
       <c r="U370" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -16141,12 +16156,12 @@
       </c>
       <c r="T371" t="inlineStr">
         <is>
-          <t>automatic pet feeder</t>
+          <t>heated</t>
         </is>
       </c>
       <c r="U371" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -16178,12 +16193,12 @@
       </c>
       <c r="T372" t="inlineStr">
         <is>
-          <t>automatic cat feeder 2 cats</t>
+          <t>large dog</t>
         </is>
       </c>
       <c r="U372" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -16215,12 +16230,12 @@
       </c>
       <c r="T373" t="inlineStr">
         <is>
-          <t>automatic cat feeder for 2 cats</t>
+          <t>wet food</t>
         </is>
       </c>
       <c r="U373" t="inlineStr">
         <is>
-          <t>negativeExact</t>
+          <t>negativePhrase</t>
         </is>
       </c>
     </row>
@@ -16252,7 +16267,7 @@
       </c>
       <c r="T374" t="inlineStr">
         <is>
-          <t>timed cat feeder</t>
+          <t>automatic cat feeder</t>
         </is>
       </c>
       <c r="U374" t="inlineStr">
@@ -16289,7 +16304,7 @@
       </c>
       <c r="T375" t="inlineStr">
         <is>
-          <t>dual cat feeder</t>
+          <t>cat feeder automatic</t>
         </is>
       </c>
       <c r="U375" t="inlineStr">
@@ -16326,7 +16341,7 @@
       </c>
       <c r="T376" t="inlineStr">
         <is>
-          <t>automatic cat feeder with camera</t>
+          <t>cat automatic feeders</t>
         </is>
       </c>
       <c r="U376" t="inlineStr">
@@ -16363,7 +16378,7 @@
       </c>
       <c r="T377" t="inlineStr">
         <is>
-          <t>cat feeder with camera</t>
+          <t>automatic pet feeder</t>
         </is>
       </c>
       <c r="U377" t="inlineStr">
@@ -16400,7 +16415,7 @@
       </c>
       <c r="T378" t="inlineStr">
         <is>
-          <t>pet feeder with camera</t>
+          <t>automatic cat feeder 2 cats</t>
         </is>
       </c>
       <c r="U378" t="inlineStr">
@@ -16437,7 +16452,7 @@
       </c>
       <c r="T379" t="inlineStr">
         <is>
-          <t>automatic dog feeder with camera</t>
+          <t>automatic cat feeder for 2 cats</t>
         </is>
       </c>
       <c r="U379" t="inlineStr">
@@ -16474,7 +16489,7 @@
       </c>
       <c r="T380" t="inlineStr">
         <is>
-          <t>wifi cat feeder</t>
+          <t>timed cat feeder</t>
         </is>
       </c>
       <c r="U380" t="inlineStr">
@@ -16511,7 +16526,7 @@
       </c>
       <c r="T381" t="inlineStr">
         <is>
-          <t>automatic cat feeder wifi</t>
+          <t>dual cat feeder</t>
         </is>
       </c>
       <c r="U381" t="inlineStr">
@@ -16548,7 +16563,7 @@
       </c>
       <c r="T382" t="inlineStr">
         <is>
-          <t>cat water fountain</t>
+          <t>automatic cat feeder with camera</t>
         </is>
       </c>
       <c r="U382" t="inlineStr">
@@ -16585,7 +16600,7 @@
       </c>
       <c r="T383" t="inlineStr">
         <is>
-          <t>stainless steel cat water fountain</t>
+          <t>cat feeder with camera</t>
         </is>
       </c>
       <c r="U383" t="inlineStr">
@@ -16622,7 +16637,7 @@
       </c>
       <c r="T384" t="inlineStr">
         <is>
-          <t>cat water fountain stainless steel</t>
+          <t>pet feeder with camera</t>
         </is>
       </c>
       <c r="U384" t="inlineStr">
@@ -16659,7 +16674,7 @@
       </c>
       <c r="T385" t="inlineStr">
         <is>
-          <t>cat fountain stainless steel</t>
+          <t>automatic dog feeder with camera</t>
         </is>
       </c>
       <c r="U385" t="inlineStr">
@@ -16696,7 +16711,7 @@
       </c>
       <c r="T386" t="inlineStr">
         <is>
-          <t>cat fountain</t>
+          <t>wifi cat feeder</t>
         </is>
       </c>
       <c r="U386" t="inlineStr">
@@ -16733,7 +16748,7 @@
       </c>
       <c r="T387" t="inlineStr">
         <is>
-          <t>water fountains for cats indoor</t>
+          <t>automatic cat feeder wifi</t>
         </is>
       </c>
       <c r="U387" t="inlineStr">
@@ -16770,7 +16785,7 @@
       </c>
       <c r="T388" t="inlineStr">
         <is>
-          <t>pet water fountain</t>
+          <t>cat water fountain</t>
         </is>
       </c>
       <c r="U388" t="inlineStr">
@@ -16807,7 +16822,7 @@
       </c>
       <c r="T389" t="inlineStr">
         <is>
-          <t>metal cat water fountain</t>
+          <t>stainless steel cat water fountain</t>
         </is>
       </c>
       <c r="U389" t="inlineStr">
@@ -16844,7 +16859,7 @@
       </c>
       <c r="T390" t="inlineStr">
         <is>
-          <t>stainless steel pet water fountain</t>
+          <t>cat water fountain stainless steel</t>
         </is>
       </c>
       <c r="U390" t="inlineStr">
@@ -16881,7 +16896,7 @@
       </c>
       <c r="T391" t="inlineStr">
         <is>
-          <t>stainless steel dog water fountain</t>
+          <t>cat fountain stainless steel</t>
         </is>
       </c>
       <c r="U391" t="inlineStr">
@@ -16918,7 +16933,7 @@
       </c>
       <c r="T392" t="inlineStr">
         <is>
-          <t>water fountain for cats</t>
+          <t>cat fountain</t>
         </is>
       </c>
       <c r="U392" t="inlineStr">
@@ -16955,7 +16970,7 @@
       </c>
       <c r="T393" t="inlineStr">
         <is>
-          <t>automatic cat water fountain</t>
+          <t>water fountains for cats indoor</t>
         </is>
       </c>
       <c r="U393" t="inlineStr">
@@ -16992,7 +17007,7 @@
       </c>
       <c r="T394" t="inlineStr">
         <is>
-          <t>cat water fountain with filter</t>
+          <t>pet water fountain</t>
         </is>
       </c>
       <c r="U394" t="inlineStr">
@@ -17029,7 +17044,7 @@
       </c>
       <c r="T395" t="inlineStr">
         <is>
-          <t>quiet cat water fountain</t>
+          <t>metal cat water fountain</t>
         </is>
       </c>
       <c r="U395" t="inlineStr">
@@ -17066,7 +17081,7 @@
       </c>
       <c r="T396" t="inlineStr">
         <is>
-          <t>small cat water fountain</t>
+          <t>stainless steel pet water fountain</t>
         </is>
       </c>
       <c r="U396" t="inlineStr">
@@ -17083,7 +17098,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -17096,23 +17111,20 @@
           <t>V2-Discovery</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>V2-Auto-Dual</t>
-        </is>
-      </c>
-      <c r="K397" t="inlineStr">
-        <is>
-          <t>Auto - Dual Feeders</t>
-        </is>
-      </c>
       <c r="O397" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="R397" t="n">
-        <v>0.4</v>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>stainless steel dog water fountain</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
       </c>
     </row>
     <row r="398">
@@ -17123,7 +17135,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -17136,19 +17148,19 @@
           <t>V2-Discovery</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr">
-        <is>
-          <t>V2-Auto-Dual</t>
-        </is>
-      </c>
       <c r="O398" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q398" t="inlineStr">
-        <is>
-          <t>LW-EZAJ-KKZD</t>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>water fountain for cats</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
         </is>
       </c>
     </row>
@@ -17160,7 +17172,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -17173,19 +17185,19 @@
           <t>V2-Discovery</t>
         </is>
       </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>V2-Auto-Dual</t>
-        </is>
-      </c>
       <c r="O399" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q399" t="inlineStr">
-        <is>
-          <t>93-E8EG-20UY</t>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>automatic cat water fountain</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
         </is>
       </c>
     </row>
@@ -17197,7 +17209,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -17210,23 +17222,20 @@
           <t>V2-Discovery</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>V2-Auto-Camera</t>
-        </is>
-      </c>
-      <c r="K400" t="inlineStr">
-        <is>
-          <t>Auto - Camera Feeder</t>
-        </is>
-      </c>
       <c r="O400" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="R400" t="n">
-        <v>0.4</v>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>cat water fountain with filter</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
       </c>
     </row>
     <row r="401">
@@ -17237,7 +17246,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -17250,19 +17259,19 @@
           <t>V2-Discovery</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>V2-Auto-Camera</t>
-        </is>
-      </c>
       <c r="O401" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q401" t="inlineStr">
-        <is>
-          <t>2H-2T1T-CJC3</t>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>quiet cat water fountain</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
         </is>
       </c>
     </row>
@@ -17274,7 +17283,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Campaign Negative Keyword</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -17287,23 +17296,20 @@
           <t>V2-Discovery</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>V2-Auto-WiFi</t>
-        </is>
-      </c>
-      <c r="K402" t="inlineStr">
-        <is>
-          <t>Auto - 5L WiFi Feeder</t>
-        </is>
-      </c>
       <c r="O402" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="R402" t="n">
-        <v>0.2</v>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>small cat water fountain</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>negativeExact</t>
+        </is>
       </c>
     </row>
     <row r="403">
@@ -17314,7 +17320,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -17329,7 +17335,12 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>V2-Auto-WiFi</t>
+          <t>V2-Auto-Dual</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Auto - Dual Feeders</t>
         </is>
       </c>
       <c r="O403" t="inlineStr">
@@ -17337,10 +17348,8 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q403" t="inlineStr">
-        <is>
-          <t>QO-7VBS-CVT4</t>
-        </is>
+      <c r="R403" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="404">
@@ -17351,7 +17360,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -17366,12 +17375,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>V2-Auto-Stainless</t>
-        </is>
-      </c>
-      <c r="K404" t="inlineStr">
-        <is>
-          <t>Auto - Stainless Fountain</t>
+          <t>V2-Auto-Dual</t>
         </is>
       </c>
       <c r="O404" t="inlineStr">
@@ -17379,8 +17383,10 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="R404" t="n">
-        <v>0.4</v>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>LW-EZAJ-KKZD</t>
+        </is>
       </c>
     </row>
     <row r="405">
@@ -17406,7 +17412,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>V2-Auto-Stainless</t>
+          <t>V2-Auto-Dual</t>
         </is>
       </c>
       <c r="O405" t="inlineStr">
@@ -17416,7 +17422,7 @@
       </c>
       <c r="Q405" t="inlineStr">
         <is>
-          <t>QY-HHE8-0H1B</t>
+          <t>93-E8EG-20UY</t>
         </is>
       </c>
     </row>
@@ -17443,12 +17449,12 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>V2-Auto-Basic</t>
+          <t>V2-Auto-Camera</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>Auto - $19.99 Fountains</t>
+          <t>Auto - Camera Feeder</t>
         </is>
       </c>
       <c r="O406" t="inlineStr">
@@ -17457,7 +17463,7 @@
         </is>
       </c>
       <c r="R406" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="407">
@@ -17483,7 +17489,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>V2-Auto-Basic</t>
+          <t>V2-Auto-Camera</t>
         </is>
       </c>
       <c r="O407" t="inlineStr">
@@ -17493,7 +17499,7 @@
       </c>
       <c r="Q407" t="inlineStr">
         <is>
-          <t>L6-L3S1-I7Q6</t>
+          <t>2H-2T1T-CJC3</t>
         </is>
       </c>
     </row>
@@ -17505,7 +17511,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -17520,7 +17526,12 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>V2-Auto-Basic</t>
+          <t>V2-Auto-WiFi</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Auto - 5L WiFi Feeder</t>
         </is>
       </c>
       <c r="O408" t="inlineStr">
@@ -17528,10 +17539,8 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q408" t="inlineStr">
-        <is>
-          <t>SD-85ET-IOZ3</t>
-        </is>
+      <c r="R408" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="409">
@@ -17557,7 +17566,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>V2-Auto-Basic</t>
+          <t>V2-Auto-WiFi</t>
         </is>
       </c>
       <c r="O409" t="inlineStr">
@@ -17567,7 +17576,7 @@
       </c>
       <c r="Q409" t="inlineStr">
         <is>
-          <t>JE-LQEW-9EHL</t>
+          <t>QO-7VBS-CVT4</t>
         </is>
       </c>
     </row>
@@ -17579,7 +17588,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -17589,36 +17598,26 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>V2-Waiting</t>
-        </is>
-      </c>
-      <c r="J410" t="inlineStr">
-        <is>
-          <t>PETME2 | Waiting For Stock | Paused</t>
-        </is>
-      </c>
-      <c r="L410" t="inlineStr">
-        <is>
-          <t>20261004</t>
-        </is>
-      </c>
-      <c r="N410" t="inlineStr">
-        <is>
-          <t>Manual</t>
+          <t>V2-Discovery</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>V2-Auto-Stainless</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Auto - Stainless Fountain</t>
         </is>
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>paused</t>
-        </is>
-      </c>
-      <c r="P410" t="n">
-        <v>2</v>
-      </c>
-      <c r="V410" t="inlineStr">
-        <is>
-          <t>Dynamic bids - down only</t>
-        </is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="R410" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="411">
@@ -17629,7 +17628,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -17639,26 +17638,23 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>V2-Waiting</t>
+          <t>V2-Discovery</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>V2-Wait-Filters</t>
-        </is>
-      </c>
-      <c r="K411" t="inlineStr">
-        <is>
-          <t>Filters (out of stock)</t>
+          <t>V2-Auto-Stainless</t>
         </is>
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>paused</t>
-        </is>
-      </c>
-      <c r="R411" t="n">
-        <v>0.25</v>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>QY-HHE8-0H1B</t>
+        </is>
       </c>
     </row>
     <row r="412">
@@ -17669,7 +17665,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -17679,12 +17675,17 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>V2-Waiting</t>
+          <t>V2-Discovery</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>V2-Wait-Filters</t>
+          <t>V2-Auto-Basic</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Auto - $19.99 Fountains</t>
         </is>
       </c>
       <c r="O412" t="inlineStr">
@@ -17692,10 +17693,8 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="Q412" t="inlineStr">
-        <is>
-          <t>2L-Filter</t>
-        </is>
+      <c r="R412" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="413">
@@ -17716,12 +17715,12 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>V2-Waiting</t>
+          <t>V2-Discovery</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>V2-Wait-Filters</t>
+          <t>V2-Auto-Basic</t>
         </is>
       </c>
       <c r="O413" t="inlineStr">
@@ -17731,7 +17730,7 @@
       </c>
       <c r="Q413" t="inlineStr">
         <is>
-          <t>2.2Ltr-Filter-Transparent</t>
+          <t>L6-L3S1-I7Q6</t>
         </is>
       </c>
     </row>
@@ -17753,12 +17752,12 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>V2-Waiting</t>
+          <t>V2-Discovery</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>V2-Wait-Filters</t>
+          <t>V2-Auto-Basic</t>
         </is>
       </c>
       <c r="O414" t="inlineStr">
@@ -17768,7 +17767,7 @@
       </c>
       <c r="Q414" t="inlineStr">
         <is>
-          <t>2.2L-Filter</t>
+          <t>SD-85ET-IOZ3</t>
         </is>
       </c>
     </row>
@@ -17790,12 +17789,12 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>V2-Waiting</t>
+          <t>V2-Discovery</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>V2-Wait-Filters</t>
+          <t>V2-Auto-Basic</t>
         </is>
       </c>
       <c r="O415" t="inlineStr">
@@ -17805,7 +17804,7 @@
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>3.2L-Stainless-Steel-Filter</t>
+          <t>JE-LQEW-9EHL</t>
         </is>
       </c>
     </row>
@@ -17817,7 +17816,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -17830,27 +17829,32 @@
           <t>V2-Waiting</t>
         </is>
       </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>V2-Wait-Filters</t>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>PETME2 | Waiting For Stock | Paused</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>20261004</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>Manual</t>
         </is>
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="S416" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T416" t="inlineStr">
-        <is>
-          <t>petme2 filter</t>
-        </is>
-      </c>
-      <c r="U416" t="inlineStr">
-        <is>
-          <t>exact</t>
+          <t>paused</t>
+        </is>
+      </c>
+      <c r="P416" t="n">
+        <v>2</v>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>Dynamic bids - down only</t>
         </is>
       </c>
     </row>
@@ -17862,7 +17866,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Ad Group</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -17880,23 +17884,18 @@
           <t>V2-Wait-Filters</t>
         </is>
       </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Filters (out of stock)</t>
+        </is>
+      </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="S417" t="n">
+          <t>paused</t>
+        </is>
+      </c>
+      <c r="R417" t="n">
         <v>0.25</v>
-      </c>
-      <c r="T417" t="inlineStr">
-        <is>
-          <t>petme2 fountain filter</t>
-        </is>
-      </c>
-      <c r="U417" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
       </c>
     </row>
     <row r="418">
@@ -17907,7 +17906,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Ad Group</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -17922,21 +17921,18 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>V2-Wait-Supplement</t>
-        </is>
-      </c>
-      <c r="K418" t="inlineStr">
-        <is>
-          <t>Supplement (out of stock)</t>
+          <t>V2-Wait-Filters</t>
         </is>
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>paused</t>
-        </is>
-      </c>
-      <c r="R418" t="n">
-        <v>0.3</v>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>2L-Filter</t>
+        </is>
       </c>
     </row>
     <row r="419">
@@ -17962,7 +17958,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>V2-Wait-Supplement</t>
+          <t>V2-Wait-Filters</t>
         </is>
       </c>
       <c r="O419" t="inlineStr">
@@ -17972,7 +17968,7 @@
       </c>
       <c r="Q419" t="inlineStr">
         <is>
-          <t>Cat-Skin-&amp;-Coat-Supplement</t>
+          <t>2.2Ltr-Filter-Transparent</t>
         </is>
       </c>
     </row>
@@ -17984,7 +17980,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -17999,7 +17995,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>V2-Wait-Supplement</t>
+          <t>V2-Wait-Filters</t>
         </is>
       </c>
       <c r="O420" t="inlineStr">
@@ -18007,17 +18003,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S420" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T420" t="inlineStr">
-        <is>
-          <t>cat skin and coat supplement</t>
-        </is>
-      </c>
-      <c r="U420" t="inlineStr">
-        <is>
-          <t>exact</t>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>2.2L-Filter</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18017,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -18044,7 +18032,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>V2-Wait-Supplement</t>
+          <t>V2-Wait-Filters</t>
         </is>
       </c>
       <c r="O421" t="inlineStr">
@@ -18052,17 +18040,9 @@
           <t>enabled</t>
         </is>
       </c>
-      <c r="S421" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T421" t="inlineStr">
-        <is>
-          <t>cat vitamins for skin and coat</t>
-        </is>
-      </c>
-      <c r="U421" t="inlineStr">
-        <is>
-          <t>exact</t>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>3.2L-Stainless-Steel-Filter</t>
         </is>
       </c>
     </row>
@@ -18089,23 +18069,280 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
+          <t>V2-Wait-Filters</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S422" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>petme2 filter</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>V2-Waiting</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>V2-Wait-Filters</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S423" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>petme2 fountain filter</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Ad Group</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>V2-Waiting</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
           <t>V2-Wait-Supplement</t>
         </is>
       </c>
-      <c r="O422" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="S422" t="n">
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Supplement (out of stock)</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>paused</t>
+        </is>
+      </c>
+      <c r="R424" t="n">
         <v>0.3</v>
       </c>
-      <c r="T422" t="inlineStr">
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Product Ad</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>V2-Waiting</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>V2-Wait-Supplement</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>Cat-Skin-&amp;-Coat-Supplement</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>V2-Waiting</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>V2-Wait-Supplement</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S426" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>cat skin and coat supplement</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>V2-Waiting</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>V2-Wait-Supplement</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S427" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>cat vitamins for skin and coat</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Sponsored Products</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>V2-Waiting</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>V2-Wait-Supplement</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="S428" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T428" t="inlineStr">
         <is>
           <t>cat shedding supplement</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="U428" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
